--- a/src/reports/metrics/consolidated_Ischaemia_efficientnet.xlsx
+++ b/src/reports/metrics/consolidated_Ischaemia_efficientnet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,154 +678,154 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0002261327455542778</v>
+        <v>0.006569969409533017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8900448678391443</v>
+        <v>0.99990772762335</v>
       </c>
       <c r="D2" t="n">
-        <v>0.883960707415783</v>
+        <v>0.9999086770908484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8140677527799328</v>
+        <v>0.9906166219839142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8056756756756757</v>
+        <v>0.9905437352245863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7795938583457157</v>
+        <v>0.9830395743265713</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8517316017316018</v>
+        <v>0.9983113812901047</v>
       </c>
       <c r="I2" t="n">
-        <v>3700</v>
+        <v>5922</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4994594594594595</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7952732817264836</v>
+        <v>0.9789135023048103</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8070154884360867</v>
+        <v>0.9782341612063465</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7116465863453815</v>
+        <v>0.9321948769462581</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7069387755102041</v>
+        <v>0.9315762797769893</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6965408805031447</v>
+        <v>0.9243027888446215</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7274220032840722</v>
+        <v>0.9402228976697061</v>
       </c>
       <c r="Q2" t="n">
-        <v>1225</v>
+        <v>1973</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4971428571428572</v>
+        <v>0.5002534211860111</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8342605033741595</v>
+        <v>0.968575284364758</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8336181453691347</v>
+        <v>0.9747365323808452</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7589090185148317</v>
+        <v>0.9102231447846393</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7551061678463094</v>
+        <v>0.9124050632911392</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7489194499017682</v>
+        <v>0.9329787234042554</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7691686844229217</v>
+        <v>0.8885511651469098</v>
       </c>
       <c r="Y2" t="n">
-        <v>4945</v>
+        <v>1975</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.5011122345803842</v>
+        <v>0.499746835443038</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.8346661548631993</v>
+        <v>0.9724871606749816</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8584832100028221</v>
+        <v>0.973345986572886</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7420814479638009</v>
+        <v>0.9186106791083463</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.7673469387755102</v>
+        <v>0.9204257475924987</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.8266129032258065</v>
+        <v>0.940552016985138</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.6732348111658456</v>
+        <v>0.8976697061803445</v>
       </c>
       <c r="AG2" t="n">
-        <v>1225</v>
+        <v>1973</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.4971428571428572</v>
+        <v>0.5002534211860111</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.8714258232887186</v>
+        <v>0.9625321487023616</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.8701043583370632</v>
+        <v>0.9709377914156428</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7708742097231306</v>
+        <v>0.9001618996222343</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.7874620829120323</v>
+        <v>0.9063291139240506</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.838311996206733</v>
+        <v>0.9630484988452656</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.7134786117836965</v>
+        <v>0.8449848024316109</v>
       </c>
       <c r="AO2" t="n">
-        <v>4945</v>
+        <v>1975</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.5011122345803842</v>
+        <v>0.499746835443038</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.03333091225318448</v>
+        <v>0.287467719443764</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1995217521771534</v>
+        <v>0.5389637180225821</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.714507905950903</v>
+        <v>32.19533240944327</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.416817149168814</v>
+        <v>12.54728991796817</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.942530078144511</v>
+        <v>7.200108982839819</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.5246239677076715</v>
+        <v>0.7087633150342947</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.445303943548594</v>
+        <v>0.19873037347273</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.07932002415907752</v>
+        <v>0.5100329415615646</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.7874620829120323</v>
+        <v>0.9063291139240506</v>
       </c>
     </row>
     <row r="3">
@@ -833,154 +833,619 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0002465504576263052</v>
+        <v>0.006004291001932141</v>
       </c>
       <c r="C3" t="n">
-        <v>0.866971451971452</v>
+        <v>0.9985243263175532</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8578034531142946</v>
+        <v>0.9984998316830676</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8034232365145229</v>
+        <v>0.978523489932886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7950243374797188</v>
+        <v>0.9783856805133401</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7714143426294821</v>
+        <v>0.972324108036012</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8382034632034632</v>
+        <v>0.9848024316109423</v>
       </c>
       <c r="I3" t="n">
-        <v>3698</v>
+        <v>5922</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4997295835586804</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8780427568109901</v>
+        <v>0.985434125411729</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8616556323559157</v>
+        <v>0.986272988191551</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7997021593447505</v>
+        <v>0.9365558912386707</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7842822774659182</v>
+        <v>0.9362025316455697</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7531556802244039</v>
+        <v>0.9309309309309309</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8523809523809524</v>
+        <v>0.9422492401215805</v>
       </c>
       <c r="Q3" t="n">
-        <v>1247</v>
+        <v>1975</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5052125100240578</v>
+        <v>0.499746835443038</v>
       </c>
       <c r="S3" t="n">
-        <v>0.813593153949718</v>
+        <v>0.9440885671950365</v>
       </c>
       <c r="T3" t="n">
-        <v>0.791346979361897</v>
+        <v>0.9505371626983993</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7476709613478691</v>
+        <v>0.8716356107660456</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7415228426395939</v>
+        <v>0.8743030917384693</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7287480680061824</v>
+        <v>0.891005291005291</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7676027676027676</v>
+        <v>0.8530901722391084</v>
       </c>
       <c r="Y3" t="n">
-        <v>4925</v>
+        <v>1973</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4988832487309645</v>
+        <v>0.5002534211860111</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8683954619124798</v>
+        <v>0.982493057521053</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8667445020645468</v>
+        <v>0.9846041638332825</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7864992150706437</v>
+        <v>0.9377551020408164</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.7818765036086608</v>
+        <v>0.9382278481012658</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.7779503105590062</v>
+        <v>0.9445015416238438</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.7952380952380952</v>
+        <v>0.9311043566362716</v>
       </c>
       <c r="AG3" t="n">
-        <v>1247</v>
+        <v>1975</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5052125100240578</v>
+        <v>0.499746835443038</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.8583026763739893</v>
+        <v>0.9353173404358075</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.8414419112313107</v>
+        <v>0.9419314149371824</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.779535648243271</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.7821319796954315</v>
+        <v>0.8692346680182463</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.7871369294605809</v>
+        <v>0.9027624309392265</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7720797720797721</v>
+        <v>0.8277608915906788</v>
       </c>
       <c r="AO3" t="n">
-        <v>4925</v>
+        <v>1973</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4988832487309645</v>
+        <v>0.5002534211860111</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.03344998653258594</v>
+        <v>0.2138214039486199</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.173519897567919</v>
+        <v>0.4336736169374857</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.504736209989662</v>
+        <v>27.5628137349491</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.617234110204744</v>
+        <v>13.20741898053886</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.78243724919633</v>
+        <v>8.490912345688267</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.5300334393810209</v>
+        <v>0.6770478392384918</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.4564379477240581</v>
+        <v>0.284201010332838</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.07359549165696277</v>
+        <v>0.3928468289056538</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.7821319796954315</v>
+        <v>0.8692346680182463</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.005988516528005974</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9980146041281225</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9980774103342868</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9767362879945661</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9768659236744344</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.98224043715847</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9712934819317798</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5922</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.951563647252337</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9577910568528116</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8698446705945367</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8769620253164557</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.9227272727272727</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8226950354609929</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1975</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9638382132016416</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.9660448180410419</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.8882950293960449</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8940699442473391</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9400452488687783</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.8419452887537994</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.5002534211860111</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.9526086082637036</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9579177884889132</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.865186789388197</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8739240506329113</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9290697674418604</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.9571015493504812</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.9597419702699119</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.8884120171673819</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.8945767866193614</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.9441277080957811</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.8389057750759878</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.5002534211860111</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.2562162029558172</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.4897850267269626</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>31.72357271212493</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>14.16104420075436</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.632027341948633</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.700825663301613</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.2616436051245655</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.4391820581770475</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.8945767866193614</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.005974592975690051</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9980390565694687</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9976979050698729</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9842598794373744</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9841216216216216</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9760876785121222</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9925700776764607</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5920</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5001689189189189</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.968248157217922</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9736291237116501</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.9144942648592284</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.9169620253164557</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.9419978517722879</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8885511651469098</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.9666350819766273</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.9682012242209174</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.8822571893651655</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.890126582278481</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9497663551401869</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.8237082066869301</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.9689413796356685</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9728798977951805</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.9007957559681697</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.9053164556962026</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.9454342984409799</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.8601823708206687</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.9598095074018927</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.9632495720911625</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.8644444444444445</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.8764556962025316</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.956949569495695</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.7882472137791287</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.2305650251148323</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.4727321909108871</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>28.93635047134722</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11.40940446724619</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9.553040528057126</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.6501559873734063</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.2549581955008923</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.395197791872514</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.8764556962025316</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.005960498273797439</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.998245319787873</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9982322559408436</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9750512645249487</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9753420030400271</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9868557592528537</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9635258358662614</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5921</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5000844451950684</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.9565423378413299</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9584104233518812</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8457207207207207</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8612658227848101</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.9518377693282636</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.7608915906788247</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1975</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.9848363066367335</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.9866871220813181</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.9373673036093418</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.9402228976697061</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9843924191750278</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.894630192502533</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1974</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.9514088002329883</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9514382520658445</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.8700380641653073</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.8789873417721519</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.9389671361502347</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.8105369807497467</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.9865310844422273</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.987645249341267</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.9428129829984544</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.9437689969604863</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.9591194968553459</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.9270516717325228</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.3044384754554494</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.5791732228557833</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>32.79118621135601</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10.22077203862733</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.172630120407817</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.7203388348654536</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.2724397144615051</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.4478991204039485</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.9437689969604863</v>
       </c>
     </row>
   </sheetData>

--- a/src/reports/metrics/consolidated_Ischaemia_efficientnet.xlsx
+++ b/src/reports/metrics/consolidated_Ischaemia_efficientnet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,154 +678,154 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.006569969409533017</v>
+        <v>0.001332155462265948</v>
       </c>
       <c r="C2" t="n">
-        <v>0.99990772762335</v>
+        <v>0.9979579231064113</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999086770908484</v>
+        <v>0.9979469136049941</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9906166219839142</v>
+        <v>0.9738276990185387</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9905437352245863</v>
+        <v>0.9740540540540541</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9830395743265713</v>
+        <v>0.9813186813186813</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9983113812901047</v>
+        <v>0.9664502164502164</v>
       </c>
       <c r="I2" t="n">
-        <v>5922</v>
+        <v>3700</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5</v>
+        <v>0.4994594594594595</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9789135023048103</v>
+        <v>0.8964344358433027</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9782341612063465</v>
+        <v>0.9261379934657562</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9321948769462581</v>
+        <v>0.8277777777777777</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9315762797769893</v>
+        <v>0.8481632653061224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9243027888446215</v>
+        <v>0.9490445859872612</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9402228976697061</v>
+        <v>0.7339901477832512</v>
       </c>
       <c r="Q2" t="n">
-        <v>1973</v>
+        <v>1225</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5002534211860111</v>
+        <v>0.4971428571428572</v>
       </c>
       <c r="S2" t="n">
-        <v>0.968575284364758</v>
+        <v>0.9540015369953606</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9747365323808452</v>
+        <v>0.9556686238893919</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9102231447846393</v>
+        <v>0.8199815837937385</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9124050632911392</v>
+        <v>0.8418604651162791</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9329787234042554</v>
+        <v>0.9544480171489818</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8885511651469098</v>
+        <v>0.7187247780468119</v>
       </c>
       <c r="Y2" t="n">
-        <v>1975</v>
+        <v>4945</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.499746835443038</v>
+        <v>0.5011122345803842</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.9724871606749816</v>
+        <v>0.9069823854306611</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.973345986572886</v>
+        <v>0.9339929774925216</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9186106791083463</v>
+        <v>0.8524886877828054</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.9204257475924987</v>
+        <v>0.866938775510204</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.940552016985138</v>
+        <v>0.9495967741935484</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.8976697061803445</v>
+        <v>0.7733990147783252</v>
       </c>
       <c r="AG2" t="n">
-        <v>1973</v>
+        <v>1225</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.5002534211860111</v>
+        <v>0.4971428571428572</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9625321487023616</v>
+        <v>0.9476610221837046</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9709377914156428</v>
+        <v>0.9511499980513904</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.9001618996222343</v>
+        <v>0.8351003834874803</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.9063291139240506</v>
+        <v>0.8521739130434782</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9630484988452656</v>
+        <v>0.9468030690537085</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8449848024316109</v>
+        <v>0.7469733656174334</v>
       </c>
       <c r="AO2" t="n">
-        <v>1975</v>
+        <v>4945</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.499746835443038</v>
+        <v>0.5011122345803842</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.287467719443764</v>
+        <v>0.1885501139432998</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.5389637180225821</v>
+        <v>0.4056912054691434</v>
       </c>
       <c r="AS2" t="n">
-        <v>32.19533240944327</v>
+        <v>24.48810279344223</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.54728991796817</v>
+        <v>11.78401662498037</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.200108982839819</v>
+        <v>8.868138104751825</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.7087633150342947</v>
+        <v>0.6331192310214533</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.19873037347273</v>
+        <v>0.2756396141382629</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.5100329415615646</v>
+        <v>0.3574796168831904</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.9063291139240506</v>
+        <v>0.8521739130434782</v>
       </c>
     </row>
     <row r="3">
@@ -833,619 +833,154 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.006004291001932141</v>
+        <v>0.001312004699654471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9985243263175532</v>
+        <v>0.9976690651690651</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9984998316830676</v>
+        <v>0.9976406841801507</v>
       </c>
       <c r="E3" t="n">
-        <v>0.978523489932886</v>
+        <v>0.9705960264900663</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9783856805133401</v>
+        <v>0.9699837750135208</v>
       </c>
       <c r="G3" t="n">
-        <v>0.972324108036012</v>
+        <v>0.9507005708354956</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9848024316109423</v>
+        <v>0.9913419913419913</v>
       </c>
       <c r="I3" t="n">
-        <v>5922</v>
+        <v>3698</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.4997295835586804</v>
       </c>
       <c r="K3" t="n">
-        <v>0.985434125411729</v>
+        <v>0.974909315427954</v>
       </c>
       <c r="L3" t="n">
-        <v>0.986272988191551</v>
+        <v>0.9785333501182302</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9365558912386707</v>
+        <v>0.9162011173184358</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9362025316455697</v>
+        <v>0.9157979149959904</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9309309309309309</v>
+        <v>0.9213483146067416</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9422492401215805</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="Q3" t="n">
-        <v>1975</v>
+        <v>1247</v>
       </c>
       <c r="R3" t="n">
-        <v>0.499746835443038</v>
+        <v>0.5052125100240578</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9440885671950365</v>
+        <v>0.959688984405354</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9505371626983993</v>
+        <v>0.9631929081974331</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8716356107660456</v>
+        <v>0.8997745439639271</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8743030917384693</v>
+        <v>0.9007106598984772</v>
       </c>
       <c r="W3" t="n">
-        <v>0.891005291005291</v>
+        <v>0.9062758051197357</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8530901722391084</v>
+        <v>0.8933658933658933</v>
       </c>
       <c r="Y3" t="n">
-        <v>1973</v>
+        <v>4925</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5002534211860111</v>
+        <v>0.4988832487309645</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.982493057521053</v>
+        <v>0.9723264130071261</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9846041638332825</v>
+        <v>0.9771229331168878</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.9377551020408164</v>
+        <v>0.9084967320261438</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.9382278481012658</v>
+        <v>0.9101844426623897</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.9445015416238438</v>
+        <v>0.936026936026936</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.9311043566362716</v>
+        <v>0.8825396825396825</v>
       </c>
       <c r="AG3" t="n">
-        <v>1975</v>
+        <v>1247</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.499746835443038</v>
+        <v>0.5052125100240578</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9353173404358075</v>
+        <v>0.9571290705812584</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9419314149371824</v>
+        <v>0.9606192278338977</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8692346680182463</v>
+        <v>0.8936040609137056</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9027624309392265</v>
+        <v>0.9278441788401948</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8277608915906788</v>
+        <v>0.8530728530728531</v>
       </c>
       <c r="AO3" t="n">
-        <v>1973</v>
+        <v>4925</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.5002534211860111</v>
+        <v>0.4988832487309645</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.2138214039486199</v>
+        <v>0.2375163673878435</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.4336736169374857</v>
+        <v>0.4724734599617713</v>
       </c>
       <c r="AS3" t="n">
-        <v>27.5628137349491</v>
+        <v>28.849971820326</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.20741898053886</v>
+        <v>11.33715869097252</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.490912345688267</v>
+        <v>9.734863763434266</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.6770478392384918</v>
+        <v>0.6814592244018672</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.284201010332838</v>
+        <v>0.2879269846671433</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3928468289056538</v>
+        <v>0.3935322397347239</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.8692346680182463</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.005988516528005974</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.9980146041281225</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9980774103342868</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9767362879945661</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9768659236744344</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.98224043715847</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9712934819317798</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5922</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.951563647252337</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.9577910568528116</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.8698446705945367</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.8769620253164557</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.9227272727272727</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.8226950354609929</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1975</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.499746835443038</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.9638382132016416</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.9660448180410419</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.8882950293960449</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.8940699442473391</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.9400452488687783</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.8419452887537994</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1973</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.5002534211860111</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.9526086082637036</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.9579177884889132</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.865186789388197</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.8739240506329113</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.9290697674418604</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1975</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.499746835443038</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.9571015493504812</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.9597419702699119</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.8884120171673819</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.8945767866193614</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.9441277080957811</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.8389057750759878</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1973</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.5002534211860111</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.2562162029558172</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.4897850267269626</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>31.72357271212493</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>14.16104420075436</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.632027341948633</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.700825663301613</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.2616436051245655</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.4391820581770475</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.8945767866193614</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.005974592975690051</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9980390565694687</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9976979050698729</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9842598794373744</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9841216216216216</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.9760876785121222</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.9925700776764607</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5920</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5001689189189189</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.968248157217922</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.9736291237116501</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.9144942648592284</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.9169620253164557</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.9419978517722879</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.8885511651469098</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1975</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.499746835443038</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.9666350819766273</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.9682012242209174</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.8822571893651655</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.890126582278481</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.9497663551401869</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.8237082066869301</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1975</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.499746835443038</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.9689413796356685</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.9728798977951805</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.9007957559681697</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.9053164556962026</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.9454342984409799</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.8601823708206687</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1975</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.499746835443038</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.9598095074018927</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.9632495720911625</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.8644444444444445</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0.8764556962025316</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.956949569495695</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0.7882472137791287</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1975</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0.499746835443038</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.2305650251148323</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.4727321909108871</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>28.93635047134722</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>11.40940446724619</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9.553040528057126</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.6501559873734063</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.2549581955008923</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.395197791872514</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.8764556962025316</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.005960498273797439</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.998245319787873</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9982322559408436</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9750512645249487</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9753420030400271</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.9868557592528537</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.9635258358662614</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5921</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5000844451950684</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.9565423378413299</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.9584104233518812</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.8457207207207207</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.8612658227848101</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.9518377693282636</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.7608915906788247</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1975</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.499746835443038</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.9848363066367335</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.9866871220813181</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.9373673036093418</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.9402228976697061</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.9843924191750278</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.894630192502533</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1974</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.9514088002329883</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.9514382520658445</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.8700380641653073</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.8789873417721519</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.9389671361502347</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.8105369807497467</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1975</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.499746835443038</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.9865310844422273</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.987645249341267</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.9428129829984544</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0.9437689969604863</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.9591194968553459</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0.9270516717325228</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1974</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.3044384754554494</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.5791732228557833</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>32.79118621135601</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>10.22077203862733</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8.172630120407817</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.7203388348654536</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.2724397144615051</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0.4478991204039485</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.9437689969604863</v>
+        <v>0.8936040609137056</v>
       </c>
     </row>
   </sheetData>

--- a/src/reports/metrics/consolidated_Ischaemia_efficientnet.xlsx
+++ b/src/reports/metrics/consolidated_Ischaemia_efficientnet.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,154 +678,154 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001332155462265948</v>
+        <v>0.006564153600565081</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9979579231064113</v>
+        <v>0.99990772762335</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9979469136049941</v>
+        <v>0.9999086770908484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9738276990185387</v>
+        <v>0.9906166219839142</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9740540540540541</v>
+        <v>0.9905437352245863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9813186813186813</v>
+        <v>0.9830395743265713</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9664502164502164</v>
+        <v>0.9983113812901047</v>
       </c>
       <c r="I2" t="n">
-        <v>3700</v>
+        <v>5922</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4994594594594595</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8964344358433027</v>
+        <v>0.9789135023048103</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9261379934657562</v>
+        <v>0.9782341612063465</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8277777777777777</v>
+        <v>0.9321948769462581</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8481632653061224</v>
+        <v>0.9315762797769893</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9490445859872612</v>
+        <v>0.9243027888446215</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7339901477832512</v>
+        <v>0.9402228976697061</v>
       </c>
       <c r="Q2" t="n">
-        <v>1225</v>
+        <v>1973</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4971428571428572</v>
+        <v>0.5002534211860111</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9540015369953606</v>
+        <v>0.968575284364758</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9556686238893919</v>
+        <v>0.9747365323808452</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8199815837937385</v>
+        <v>0.9102231447846393</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8418604651162791</v>
+        <v>0.9124050632911392</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9544480171489818</v>
+        <v>0.9329787234042554</v>
       </c>
       <c r="X2" t="n">
-        <v>0.7187247780468119</v>
+        <v>0.8885511651469098</v>
       </c>
       <c r="Y2" t="n">
-        <v>4945</v>
+        <v>1975</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.5011122345803842</v>
+        <v>0.499746835443038</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.9069823854306611</v>
+        <v>0.9724871606749816</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9339929774925216</v>
+        <v>0.973345986572886</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8524886877828054</v>
+        <v>0.9186106791083463</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.866938775510204</v>
+        <v>0.9204257475924987</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.9495967741935484</v>
+        <v>0.940552016985138</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.7733990147783252</v>
+        <v>0.8976697061803445</v>
       </c>
       <c r="AG2" t="n">
-        <v>1225</v>
+        <v>1973</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.4971428571428572</v>
+        <v>0.5002534211860111</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9476610221837046</v>
+        <v>0.9625321487023616</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9511499980513904</v>
+        <v>0.9709377914156428</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8351003834874803</v>
+        <v>0.9001618996222343</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8521739130434782</v>
+        <v>0.9063291139240506</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9468030690537085</v>
+        <v>0.9630484988452656</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.7469733656174334</v>
+        <v>0.8449848024316109</v>
       </c>
       <c r="AO2" t="n">
-        <v>4945</v>
+        <v>1975</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.5011122345803842</v>
+        <v>0.499746835443038</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.1885501139432998</v>
+        <v>0.287467719443764</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.4056912054691434</v>
+        <v>0.5389637180225821</v>
       </c>
       <c r="AS2" t="n">
-        <v>24.48810279344223</v>
+        <v>32.19533240944327</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.78401662498037</v>
+        <v>12.54728991796817</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.868138104751825</v>
+        <v>7.200108982839819</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.6331192310214533</v>
+        <v>0.7087633150342947</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2756396141382629</v>
+        <v>0.19873037347273</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.3574796168831904</v>
+        <v>0.5100329415615646</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.8521739130434782</v>
+        <v>0.9063291139240506</v>
       </c>
     </row>
     <row r="3">
@@ -833,154 +833,619 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001312004699654471</v>
+        <v>0.005840188112628345</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9976690651690651</v>
+        <v>0.9979580316944778</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9976406841801507</v>
+        <v>0.9978201035359067</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9705960264900663</v>
+        <v>0.9756429909725771</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9699837750135208</v>
+        <v>0.9758527524484971</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9507005708354956</v>
+        <v>0.9841924398625429</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9913419913419913</v>
+        <v>0.9672407970280311</v>
       </c>
       <c r="I3" t="n">
-        <v>3698</v>
+        <v>5922</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4997295835586804</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.974909315427954</v>
+        <v>0.9856422972324429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9785333501182302</v>
+        <v>0.9859652962179977</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9162011173184358</v>
+        <v>0.9283135636926251</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9157979149959904</v>
+        <v>0.929620253164557</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9213483146067416</v>
+        <v>0.9453781512605042</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9111111111111111</v>
+        <v>0.9118541033434651</v>
       </c>
       <c r="Q3" t="n">
-        <v>1247</v>
+        <v>1975</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5052125100240578</v>
+        <v>0.499746835443038</v>
       </c>
       <c r="S3" t="n">
-        <v>0.959688984405354</v>
+        <v>0.939502580195688</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9631929081974331</v>
+        <v>0.9507736640354505</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8997745439639271</v>
+        <v>0.8568306010928962</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9007106598984772</v>
+        <v>0.8672072985301571</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9062758051197357</v>
+        <v>0.930011862396204</v>
       </c>
       <c r="X3" t="n">
-        <v>0.8933658933658933</v>
+        <v>0.7943262411347518</v>
       </c>
       <c r="Y3" t="n">
-        <v>4925</v>
+        <v>1973</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4988832487309645</v>
+        <v>0.5002534211860111</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.9723264130071261</v>
+        <v>0.9850885396798051</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9771229331168878</v>
+        <v>0.985375405091738</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.9084967320261438</v>
+        <v>0.9183040330920372</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.9101844426623897</v>
+        <v>0.92</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.936026936026936</v>
+        <v>0.9376979936642027</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.8825396825396825</v>
+        <v>0.8996960486322189</v>
       </c>
       <c r="AG3" t="n">
-        <v>1247</v>
+        <v>1975</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5052125100240578</v>
+        <v>0.499746835443038</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.9571290705812584</v>
+        <v>0.9443803933899313</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9606192278338977</v>
+        <v>0.9516731225389059</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8675603217158177</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8936040609137056</v>
+        <v>0.8748099341104917</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9278441788401948</v>
+        <v>0.9214123006833713</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8530728530728531</v>
+        <v>0.8196555217831814</v>
       </c>
       <c r="AO3" t="n">
-        <v>4925</v>
+        <v>1973</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4988832487309645</v>
+        <v>0.5002534211860111</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.2375163673878435</v>
+        <v>0.2144098471414767</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.4724734599617713</v>
+        <v>0.4238549655613678</v>
       </c>
       <c r="AS3" t="n">
-        <v>28.849971820326</v>
+        <v>28.34167930810778</v>
       </c>
       <c r="AT3" t="n">
-        <v>11.33715869097252</v>
+        <v>13.31432418318543</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.734863763434266</v>
+        <v>9.560122928014497</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.6814592244018672</v>
+        <v>0.6662024737774991</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2879269846671433</v>
+        <v>0.2830463560893367</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3935322397347239</v>
+        <v>0.3831561176881624</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.8936040609137056</v>
+        <v>0.8748099341104917</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.005960500103596254</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.9977474818708733</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9977737640624188</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9756670582312469</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9755150287065181</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9696464309539693</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9817629179331308</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5922</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9588845271935977</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9644476801598676</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8916537065837221</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8941772151898734</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.9129511677282378</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8713272543059777</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1975</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9669640416694926</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.9667717431981542</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.9010309278350516</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9026862645717182</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9171038824763903</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.8855116514690983</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.5002534211860111</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.954679046224399</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9615553616355083</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.8778135048231511</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8845569620253164</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.931740614334471</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.8297872340425532</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.9526789439179928</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.9561754350799584</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.8629989212513485</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.8712620375063356</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.922722029988466</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.8105369807497467</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.5002534211860111</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.2520296411055752</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.4722546320020863</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>31.44241543935468</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>12.76699147415776</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10.08857331401191</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.6845807760799977</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.2730277196367697</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.411553056443228</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.8712620375063356</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.006104409451331889</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.99840497151262</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9983592336055873</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9816115011701771</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.981418918918919</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9718636213174445</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9915569064505235</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5920</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5001689189189189</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9635709568520319</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9688281500456571</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.9070866141732283</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.9103797468354431</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8753799392097265</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.9655921719191598</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.9673105177691775</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.8853161843515541</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.8916455696202532</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9397042093287827</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.8368794326241135</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.9621168305378832</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9654443873851376</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.8913978494623656</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.8977215189873418</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.9495990836197021</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.839918946301925</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.9640836953266965</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.9659731230992604</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.8756164383561644</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.8850632911392405</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.9534606205250596</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.2337218970429159</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.4676754059140822</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>29.26541707636591</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>11.51910398723493</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10.15009593177986</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.6609318831402354</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.2509364299785544</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.409995453161681</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.8850632911392405</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.00612147932705367</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9984327792838431</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9984067057534459</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.968811556139199</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9679108258740078</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9425103800702651</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9966227625802094</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5921</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5000844451950684</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.9506776351681168</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9441862953413976</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.8804515135967163</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8820253164556962</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.8918918918918919</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8693009118541033</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1975</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.981797819474855</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.9845499590198257</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.9398686205154119</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.9397163120567376</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.9422492401215805</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1974</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.9431649910373314</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9407741237929993</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.8633171258779039</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.8718987341772152</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.9247685185185185</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1975</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.499746835443038</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.9825985019026473</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.9851210952595181</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.9336143308746049</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.9361702127659575</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.9725576289791438</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.8976697061803445</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1974</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.2887305290842121</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.5751029253582306</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>30.83704284902297</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.145174168202127</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>10.24087442555457</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.7028904001859265</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.2671079523414346</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.4357824478444919</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.9361702127659575</v>
       </c>
     </row>
   </sheetData>
